--- a/docs/AppBase_TongHop.xlsx
+++ b/docs/AppBase_TongHop.xlsx
@@ -13,24 +13,26 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Luồng chính" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cách dùng base" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cấu hình build" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lệnh Gradle" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kiểm thử" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quy ước &amp; bẫy" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checklist app mới" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Việc còn lại" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lịch sử" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="API Worker" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lệnh Gradle" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kiểm thử" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quy ước &amp; bẫy" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checklist app mới" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Việc còn lại" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lịch sử" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Cấu trúc code'!$A$1:$D$62</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Thư viện'!$A$1:$E$34</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Luồng chính'!$A$1:$D$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Cách dùng base'!$A$1:$C$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Cấu hình build'!$A$1:$D$21</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Lệnh Gradle'!$A$1:$C$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Kiểm thử'!$A$1:$D$21</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Quy ước &amp; bẫy'!$A$1:$C$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Việc còn lại'!$A$1:$D$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Lịch sử'!$A$1:$D$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Cấu trúc code'!$A$1:$D$81</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Thư viện'!$A$1:$E$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Luồng chính'!$A$1:$D$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Cách dùng base'!$A$1:$C$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Cấu hình build'!$A$1:$D$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'API Worker'!$A$1:$E$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Lệnh Gradle'!$A$1:$C$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Kiểm thử'!$A$1:$D$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Quy ước &amp; bẫy'!$A$1:$C$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Việc còn lại'!$A$1:$D$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Lịch sử'!$A$1:$D$10</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -537,7 +539,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -554,7 +556,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Base Android để clone cho các app solo phát hành trên CH Play. Cập nhật theo code ngày 2026-10-26.</t>
+          <t>Base Android + Worker AI để clone cho các app solo phát hành trên CH Play. Cập nhật theo code ngày 2026-10-26 (gồm giai đoạn B: phiên ẩn danh, Cloudflare Worker).</t>
         </is>
       </c>
     </row>
@@ -598,234 +600,257 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>Clean Architecture (core / data / domain / feature) + MVVM, single module</t>
+          <t>Clean Architecture (core / data / domain / feature) + MVVM, single module; backend AI: Cloudflare Worker (worker/)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>Dependency injection</t>
+          <t>Danh tính</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>Koin 4.1.1</t>
+          <t>Phiên ẩn danh tự động (Firebase Anonymous Auth); đăng nhập/tạo tài khoản tuỳ chọn</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>SDK</t>
+          <t>Dependency injection</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>minSdk 24 · targetSdk 36 · compileSdk 36.1</t>
+          <t>Koin 4.1.1</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>Build</t>
+          <t>SDK</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>AGP 9.2.1 · Gradle 9.4.1 · bytecode Java 17</t>
+          <t>minSdk 24 · targetSdk 36 · compileSdk 36.1</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
+          <t>Build</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>AGP 9.2.1 · Gradle 9.4.1 · bytecode Java 17</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
           <t>Biến thể</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B12" s="6" t="inlineStr">
         <is>
           <t>Flavor mock / dev / prod × build type debug / release (không có mockRelease)</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>Số liệu (tự tính từ các sheet)</t>
         </is>
       </c>
-      <c r="B12" s="4" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="B13" s="4" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>Số file / nhóm file trong Cấu trúc code</t>
         </is>
       </c>
-      <c r="B13" s="6">
+      <c r="B14" s="6">
         <f>COUNTA('Cấu trúc code'!C2:C200)</f>
         <v/>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>Số thư viện chính</t>
         </is>
       </c>
-      <c r="B14" s="6">
+      <c r="B15" s="6">
         <f>COUNTA('Thư viện'!B2:B200)</f>
         <v/>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>Số unit test</t>
-        </is>
-      </c>
-      <c r="B15" s="6">
-        <f>'Kiểm thử'!C22</f>
-        <v/>
-      </c>
-    </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
+          <t>Số test (app + Worker)</t>
+        </is>
+      </c>
+      <c r="B16" s="6">
+        <f>'Kiểm thử'!C32</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
           <t>Tiến độ checklist app mới</t>
         </is>
       </c>
-      <c r="B16" s="7">
+      <c r="B17" s="7">
         <f>'Checklist app mới'!B2</f>
         <v/>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>Mục lục</t>
         </is>
       </c>
-      <c r="B18" s="4" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="8">
+      <c r="B19" s="4" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="8">
         <f>HYPERLINK("#'Cấu trúc code'!A1","Cấu trúc code")</f>
         <v/>
       </c>
-      <c r="B19" s="9" t="inlineStr">
+      <c r="B20" s="9" t="inlineStr">
         <is>
           <t>Từng package/file và vai trò</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="8">
+    <row r="21">
+      <c r="A21" s="8">
         <f>HYPERLINK("#'Thư viện'!A1","Thư viện")</f>
         <v/>
       </c>
-      <c r="B20" s="9" t="inlineStr">
+      <c r="B21" s="9" t="inlineStr">
         <is>
           <t>Thư viện, phiên bản, lý do chọn</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="8">
+    <row r="22">
+      <c r="A22" s="8">
         <f>HYPERLINK("#'Luồng chính'!A1","Luồng chính")</f>
         <v/>
       </c>
-      <c r="B21" s="9" t="inlineStr">
+      <c r="B22" s="9" t="inlineStr">
         <is>
           <t>Các luồng chạy quan trọng theo từng bước</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="8">
+    <row r="23">
+      <c r="A23" s="8">
         <f>HYPERLINK("#'Cách dùng base'!A1","Cách dùng base")</f>
         <v/>
       </c>
-      <c r="B22" s="9" t="inlineStr">
+      <c r="B23" s="9" t="inlineStr">
         <is>
           <t>Làm việc X thì sửa ở đâu, theo mẫu nào</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="8">
+    <row r="24">
+      <c r="A24" s="8">
         <f>HYPERLINK("#'Cấu hình build'!A1","Cấu hình build")</f>
         <v/>
       </c>
-      <c r="B23" s="9" t="inlineStr">
+      <c r="B24" s="9" t="inlineStr">
         <is>
           <t>Flavor, build type, BuildConfig, gradle.properties, ký app</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="8">
+    <row r="25">
+      <c r="A25" s="8">
+        <f>HYPERLINK("#'API Worker'!A1","API Worker")</f>
+        <v/>
+      </c>
+      <c r="B25" s="9" t="inlineStr">
+        <is>
+          <t>Endpoint, mã lỗi Worker và cách app xử lý</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="8">
         <f>HYPERLINK("#'Lệnh Gradle'!A1","Lệnh Gradle")</f>
         <v/>
       </c>
-      <c r="B24" s="9" t="inlineStr">
+      <c r="B26" s="9" t="inlineStr">
         <is>
           <t>Lệnh hay dùng</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="8">
+    <row r="27">
+      <c r="A27" s="8">
         <f>HYPERLINK("#'Kiểm thử'!A1","Kiểm thử")</f>
         <v/>
       </c>
-      <c r="B25" s="9" t="inlineStr">
+      <c r="B27" s="9" t="inlineStr">
         <is>
           <t>Danh sách test và phạm vi</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="8">
+    <row r="28">
+      <c r="A28" s="8">
         <f>HYPERLINK("#'Quy ước &amp; bẫy'!A1","Quy ước &amp; bẫy")</f>
         <v/>
       </c>
-      <c r="B26" s="9" t="inlineStr">
+      <c r="B28" s="9" t="inlineStr">
         <is>
           <t>Quy tắc phải nhớ và lý do</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="8">
+    <row r="29">
+      <c r="A29" s="8">
         <f>HYPERLINK("#'Checklist app mới'!A1","Checklist app mới")</f>
         <v/>
       </c>
-      <c r="B27" s="9" t="inlineStr">
+      <c r="B29" s="9" t="inlineStr">
         <is>
           <t>Các bước khi clone sang app mới (có cột để đánh dấu)</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="8">
+    <row r="30">
+      <c r="A30" s="8">
         <f>HYPERLINK("#'Việc còn lại'!A1","Việc còn lại")</f>
         <v/>
       </c>
-      <c r="B28" s="9" t="inlineStr">
+      <c r="B30" s="9" t="inlineStr">
         <is>
           <t>Hạng mục chưa làm / đang hoãn</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="8">
+    <row r="31">
+      <c r="A31" s="8">
         <f>HYPERLINK("#'Lịch sử'!A1","Lịch sử")</f>
         <v/>
       </c>
-      <c r="B29" s="9" t="inlineStr">
+      <c r="B31" s="9" t="inlineStr">
         <is>
           <t>Các commit chính</t>
         </is>
@@ -842,7 +867,380 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:C21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
+    <col width="66" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="10" t="inlineStr">
+        <is>
+          <t>Chủ đề</t>
+        </is>
+      </c>
+      <c r="B1" s="10" t="inlineStr">
+        <is>
+          <t>Quy tắc</t>
+        </is>
+      </c>
+      <c r="C1" s="10" t="inlineStr">
+        <is>
+          <t>Vì sao</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="11" t="inlineStr">
+        <is>
+          <t>Dữ liệu</t>
+        </is>
+      </c>
+      <c r="B2" s="12" t="inlineStr">
+        <is>
+          <t>AppPreferences chỉ thêm field vào cuối, luôn có giá trị mặc định.</t>
+        </is>
+      </c>
+      <c r="C2" s="12" t="inlineStr">
+        <is>
+          <t>ProtoBuf đánh số field theo thứ tự; đổi thứ tự làm hỏng dữ liệu người dùng.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>Dữ liệu</t>
+        </is>
+      </c>
+      <c r="B3" s="13" t="inlineStr">
+        <is>
+          <t>Đổi schema Room phải có Migration + test.</t>
+        </is>
+      </c>
+      <c r="C3" s="13" t="inlineStr">
+        <is>
+          <t>Migration sai làm crash app với mọi người dùng cũ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>Lỗi</t>
+        </is>
+      </c>
+      <c r="B4" s="12" t="inlineStr">
+        <is>
+          <t>Không hiển thị Throwable.message cho người dùng; dùng AppError + toUserMessage().</t>
+        </is>
+      </c>
+      <c r="C4" s="12" t="inlineStr">
+        <is>
+          <t>Thông báo chưa dịch, lộ chi tiết kỹ thuật.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>Coroutine</t>
+        </is>
+      </c>
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>Dùng suspendRunCatching, không dùng runCatching trong hàm suspend.</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
+          <t>runCatching nuốt CancellationException.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>Bảo mật</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>Token chỉ nằm trong DataStore mã hoá; không log header Authorization.</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>Bảo mật</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>Không commit keystore, keystore.properties, google-services.json.</t>
+        </is>
+      </c>
+      <c r="C7" s="13" t="inlineStr">
+        <is>
+          <t>Đã có trong .gitignore.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="11" t="inlineStr">
+        <is>
+          <t>Quảng cáo</t>
+        </is>
+      </c>
+      <c r="B8" s="12" t="inlineStr">
+        <is>
+          <t>Bản debug luôn dùng ID quảng cáo test.</t>
+        </is>
+      </c>
+      <c r="C8" s="12" t="inlineStr">
+        <is>
+          <t>Tự click quảng cáo thật có thể bị khoá tài khoản AdMob.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>Quảng cáo</t>
+        </is>
+      </c>
+      <c r="B9" s="13" t="inlineStr">
+        <is>
+          <t>Không hiện quảng cáo xen kẽ lúc mở app hay giữa thao tác.</t>
+        </is>
+      </c>
+      <c r="C9" s="13" t="inlineStr">
+        <is>
+          <t>Vi phạm chính sách, kéo điểm đánh giá xuống.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="13" t="inlineStr">
+        <is>
+          <t>Quảng cáo</t>
+        </is>
+      </c>
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>Manifest luôn phải có App ID AdMob.</t>
+        </is>
+      </c>
+      <c r="C10" s="13" t="inlineStr">
+        <is>
+          <t>Thiếu thì app crash ngay khi khởi động.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t>Đánh giá</t>
+        </is>
+      </c>
+      <c r="B11" s="12" t="inlineStr">
+        <is>
+          <t>Không gắn In-App Review vào nút bấm.</t>
+        </is>
+      </c>
+      <c r="C11" s="12" t="inlineStr">
+        <is>
+          <t>Google có hạn mức, hộp thoại có thể không hiện.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="11" t="inlineStr">
+        <is>
+          <t>Compose</t>
+        </is>
+      </c>
+      <c r="B12" s="12" t="inlineStr">
+        <is>
+          <t>Composable công khai phải nhận modifier; callback đặt tên thì hiện tại (onLoginSuccess, không onAuthenticated).</t>
+        </is>
+      </c>
+      <c r="C12" s="12" t="inlineStr">
+        <is>
+          <t>Luật Compose của ktlint bắt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="11" t="inlineStr">
+        <is>
+          <t>DI</t>
+        </is>
+      </c>
+      <c r="B13" s="12" t="inlineStr">
+        <is>
+          <t>Thêm ViewModel nhớ khai báo viewModelOf(...).</t>
+        </is>
+      </c>
+      <c r="C13" s="12" t="inlineStr">
+        <is>
+          <t>KoinModulesTest không bắt được lỗi quên khai báo ViewModel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="11" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+      <c r="B14" s="12" t="inlineStr">
+        <is>
+          <t>Không nâng Compose BOM lên bản dùng Compose 1.12+ khi chưa nâng compileSdk 37.</t>
+        </is>
+      </c>
+      <c r="C14" s="12" t="inlineStr">
+        <is>
+          <t>Build lỗi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="13" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+      <c r="B15" s="13" t="inlineStr">
+        <is>
+          <t>detekt 1.23.8 cần đoạn ghim Kotlin riêng trong build.gradle.kts.</t>
+        </is>
+      </c>
+      <c r="C15" s="13" t="inlineStr">
+        <is>
+          <t>Bỏ đoạn đó thì detekt lỗi với Kotlin 2.2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="11" t="inlineStr">
+        <is>
+          <t>Thiết bị</t>
+        </is>
+      </c>
+      <c r="B16" s="12" t="inlineStr">
+        <is>
+          <t>Không dùng emulator (chưa cài); hỏi trước khi chạy trên điện thoại.</t>
+        </is>
+      </c>
+      <c r="C16" s="12" t="inlineStr">
+        <is>
+          <t>Thoả thuận khi làm việc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="11" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="B17" s="12" t="inlineStr">
+        <is>
+          <t>App không chứa key AI và không gửi prompt; prompt/schema/model nằm ở Worker.</t>
+        </is>
+      </c>
+      <c r="C17" s="12" t="inlineStr">
+        <is>
+          <t>Key trong APK bị lấy ra trong vài phút.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="13" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="B18" s="13" t="inlineStr">
+        <is>
+          <t>Mọi task phải cho phép trả lời "không nhận diện được"; app và Worker cùng kiểm tra schema.</t>
+        </is>
+      </c>
+      <c r="C18" s="13" t="inlineStr">
+        <is>
+          <t>AI có thể trả lời tự tin cho ảnh không liên quan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="13" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="B19" s="13" t="inlineStr">
+        <is>
+          <t>Tính năng AI cần FirebaseAuthBackend.</t>
+        </is>
+      </c>
+      <c r="C19" s="13" t="inlineStr">
+        <is>
+          <t>Worker chỉ xác minh Firebase ID token.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="11" t="inlineStr">
+        <is>
+          <t>Quyền</t>
+        </is>
+      </c>
+      <c r="B20" s="12" t="inlineStr">
+        <is>
+          <t>Không khai báo quyền CAMERA.</t>
+        </is>
+      </c>
+      <c r="C20" s="12" t="inlineStr">
+        <is>
+          <t>Khai báo thì TakePicture bắt người dùng cấp quyền.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="11" t="inlineStr">
+        <is>
+          <t>App Check</t>
+        </is>
+      </c>
+      <c r="B21" s="12" t="inlineStr">
+        <is>
+          <t>Bản debug: đăng ký debug token từ logcat; prod: APP_CHECK_MODE = enforce.</t>
+        </is>
+      </c>
+      <c r="C21" s="12" t="inlineStr">
+        <is>
+          <t>Không có token hợp lệ thì Worker trả 403.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:C21"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -865,7 +1263,7 @@
         </is>
       </c>
       <c r="B2" s="18">
-        <f>IFERROR(COUNTIF(D6:D18,"Xong")/COUNTA(B6:B18),0)</f>
+        <f>IFERROR(COUNTIF(D6:D19,"Xong")/COUNTA(B6:B19),0)</f>
         <v/>
       </c>
     </row>
@@ -1044,12 +1442,12 @@
       </c>
       <c r="B13" s="13" t="inlineStr">
         <is>
-          <t>Đặt lời gọi rememberInAppReview() ở khoảnh khắc tích cực thật</t>
+          <t>Viết task AI cho app (Worker + data class + mẫu fake), deploy Worker</t>
         </is>
       </c>
       <c r="C13" s="13" t="inlineStr">
         <is>
-          <t>Màn hình tính năng</t>
+          <t>worker/src/tasks/, feature/</t>
         </is>
       </c>
       <c r="D13" s="20" t="inlineStr">
@@ -1064,12 +1462,12 @@
       </c>
       <c r="B14" s="13" t="inlineStr">
         <is>
-          <t>Quyết định kiếm tiền: bật ads.enabled + ID thật, hoặc gỡ bỏ phần monetization</t>
+          <t>Đặt lời gọi rememberInAppReview() ở khoảnh khắc tích cực thật</t>
         </is>
       </c>
       <c r="C14" s="13" t="inlineStr">
         <is>
-          <t>gradle.properties</t>
+          <t>Màn hình tính năng</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -1084,12 +1482,12 @@
       </c>
       <c r="B15" s="13" t="inlineStr">
         <is>
-          <t>Tạo keystore, cấu hình ký release</t>
+          <t>Quyết định kiếm tiền: bật ads.enabled + ID thật, hoặc gỡ bỏ phần monetization</t>
         </is>
       </c>
       <c r="C15" s="13" t="inlineStr">
         <is>
-          <t>keystore.properties / SIGNING_* trên CI</t>
+          <t>gradle.properties</t>
         </is>
       </c>
       <c r="D15" s="20" t="inlineStr">
@@ -1104,12 +1502,12 @@
       </c>
       <c r="B16" s="13" t="inlineStr">
         <is>
-          <t>Tạo app trên Play Console, track Internal testing</t>
+          <t>Tạo keystore, cấu hình ký release</t>
         </is>
       </c>
       <c r="C16" s="13" t="inlineStr">
         <is>
-          <t>Play Console</t>
+          <t>keystore.properties / SIGNING_* trên CI</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -1124,7 +1522,7 @@
       </c>
       <c r="B17" s="13" t="inlineStr">
         <is>
-          <t>Privacy policy, Data safety form, nội dung trang CH Play</t>
+          <t>Tạo app trên Play Console, track Internal testing</t>
         </is>
       </c>
       <c r="C17" s="13" t="inlineStr">
@@ -1144,15 +1542,35 @@
       </c>
       <c r="B18" s="13" t="inlineStr">
         <is>
+          <t>Privacy policy, Data safety form, nội dung trang CH Play</t>
+        </is>
+      </c>
+      <c r="C18" s="13" t="inlineStr">
+        <is>
+          <t>Play Console</t>
+        </is>
+      </c>
+      <c r="D18" s="20" t="inlineStr">
+        <is>
+          <t>Chưa</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="13" t="n">
+        <v>14</v>
+      </c>
+      <c r="B19" s="13" t="inlineStr">
+        <is>
           <t>Chạy kiểm tra đầy đủ và build bundleProdRelease</t>
         </is>
       </c>
-      <c r="C18" s="13" t="inlineStr">
+      <c r="C19" s="13" t="inlineStr">
         <is>
           <t>Terminal / CI</t>
         </is>
       </c>
-      <c r="D18" s="20" t="inlineStr">
+      <c r="D19" s="20" t="inlineStr">
         <is>
           <t>Chưa</t>
         </is>
@@ -1160,7 +1578,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="D6 D7 D8 D9 D10 D11 D12 D13 D14 D15 D16 D17 D18" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="D6 D7 D8 D9 D10 D11 D12 D13 D14 D15 D16 D17 D18 D19" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Chưa,Xong"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1168,7 +1586,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1208,34 +1626,34 @@
     <row r="2">
       <c r="A2" s="13" t="inlineStr">
         <is>
-          <t>Baseline Profile</t>
+          <t>Deploy Worker + thử thật</t>
         </is>
       </c>
       <c r="B2" s="13" t="inlineStr">
         <is>
-          <t>Module :baselineprofile, sinh profile từ prodRelease (cần máy API 33+).</t>
+          <t>Tạo Firebase project, D1, secret Gemini; deploy env dev; chạy devDebug trên máy.</t>
         </is>
       </c>
       <c r="C2" s="13" t="inlineStr">
         <is>
-          <t>Trung bình</t>
+          <t>Cao</t>
         </is>
       </c>
       <c r="D2" s="13" t="inlineStr">
         <is>
-          <t>Hoãn tới khi cài emulator và app có màn hình thật.</t>
+          <t>Hướng dẫn trong worker/README.md; cần tài khoản của bạn.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="13" t="inlineStr">
         <is>
-          <t>Commit phần kiếm tiền</t>
+          <t>Commit giai đoạn B</t>
         </is>
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>AdMob + UMP + Billing đang ở working tree, chưa commit.</t>
+          <t>Phiên ẩn danh + thư mục worker/ chưa commit.</t>
         </is>
       </c>
       <c r="C3" s="13" t="inlineStr">
@@ -1253,7 +1671,7 @@
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>.github/workflows/android.yml đang bị ignore nên chưa từng được commit.</t>
+          <t>.github/workflows/android.yml (đã có job worker) vẫn bị ignore.</t>
         </is>
       </c>
       <c r="C4" s="13" t="inlineStr">
@@ -1263,63 +1681,63 @@
       </c>
       <c r="D4" s="13" t="inlineStr">
         <is>
-          <t>Xoá dòng tương ứng trong .gitignore nếu muốn CI chạy.</t>
+          <t>Xoá dòng tương ứng trong .gitignore để CI chạy.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="13" t="inlineStr">
         <is>
-          <t>Gửi FCM token lên server</t>
+          <t>Data safety trên Play Console</t>
         </is>
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>Hiện chỉ lưu local; cần khi gửi push theo từng người dùng.</t>
+          <t>Khai báo: gửi ảnh lên server (AI), AD_ID (AdMob), tài khoản ẩn danh.</t>
         </is>
       </c>
       <c r="C5" s="13" t="inlineStr">
         <is>
-          <t>Thấp</t>
+          <t>Cao</t>
         </is>
       </c>
       <c r="D5" s="13" t="inlineStr">
         <is>
-          <t>Khi có backend.</t>
+          <t>Trước khi phát hành.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="13" t="inlineStr">
         <is>
-          <t>HomeViewModel gọi thẳng AppDataStore</t>
+          <t>Baseline Profile</t>
         </is>
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>Chưa qua domain cho cài đặt theme.</t>
+          <t>Module :baselineprofile, sinh profile từ prodRelease.</t>
         </is>
       </c>
       <c r="C6" s="13" t="inlineStr">
         <is>
-          <t>Thấp</t>
+          <t>Trung bình</t>
         </is>
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>Chấp nhận được với app solo.</t>
+          <t>Hoãn tới khi cài emulator.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="13" t="inlineStr">
         <is>
-          <t>Xác minh giao dịch trên server</t>
+          <t>App Check chống dùng lại token</t>
         </is>
       </c>
       <c r="B7" s="13" t="inlineStr">
         <is>
-          <t>Billing đang xác minh phía client.</t>
+          <t>Dùng limited-use token + xác minh qua App Check API ở Worker.</t>
         </is>
       </c>
       <c r="C7" s="13" t="inlineStr">
@@ -1329,19 +1747,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>Cần nếu bán thứ giá trị cao / gói đăng ký.</t>
+          <t>Khi AI tốn nhiều tiền.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="13" t="inlineStr">
         <is>
-          <t>Nâng detekt 2.0</t>
+          <t>Gửi FCM token lên server</t>
         </is>
       </c>
       <c r="B8" s="13" t="inlineStr">
         <is>
-          <t>Bỏ đoạn ghim Kotlin khi detekt 2.0 ổn định.</t>
+          <t>Hiện chỉ lưu local.</t>
         </is>
       </c>
       <c r="C8" s="13" t="inlineStr">
@@ -1349,17 +1767,21 @@
           <t>Thấp</t>
         </is>
       </c>
-      <c r="D8" s="13" t="inlineStr"/>
+      <c r="D8" s="13" t="inlineStr">
+        <is>
+          <t>Có thể dùng Worker.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="13" t="inlineStr">
         <is>
-          <t>Nâng compileSdk 37</t>
+          <t>Xác minh giao dịch Billing trên server</t>
         </is>
       </c>
       <c r="B9" s="13" t="inlineStr">
         <is>
-          <t>Cần trước khi nâng Compose BOM có Compose 1.12+.</t>
+          <t>Đang xác minh phía client.</t>
         </is>
       </c>
       <c r="C9" s="13" t="inlineStr">
@@ -1367,29 +1789,29 @@
           <t>Thấp</t>
         </is>
       </c>
-      <c r="D9" s="13" t="inlineStr"/>
+      <c r="D9" s="13" t="inlineStr">
+        <is>
+          <t>Có thể dùng Worker.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="13" t="inlineStr">
         <is>
-          <t>Thử thật trên Google Play</t>
+          <t>Nâng detekt 2.0 / compileSdk 37</t>
         </is>
       </c>
       <c r="B10" s="13" t="inlineStr">
         <is>
-          <t>In-App Review/Update, Billing chỉ thử được qua Internal testing.</t>
+          <t>Bỏ đoạn ghim Kotlin của detekt; nâng compileSdk trước khi lên Compose 1.12+.</t>
         </is>
       </c>
       <c r="C10" s="13" t="inlineStr">
         <is>
-          <t>Trung bình</t>
-        </is>
-      </c>
-      <c r="D10" s="13" t="inlineStr">
-        <is>
-          <t>Khi app đầu tiên lên Play Console.</t>
-        </is>
-      </c>
+          <t>Thấp</t>
+        </is>
+      </c>
+      <c r="D10" s="13" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:D10"/>
@@ -1397,13 +1819,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1543,27 +1965,85 @@
     <row r="7">
       <c r="A7" s="13" t="inlineStr">
         <is>
+          <t>5d4da2a</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="C7" s="13" t="inlineStr">
+        <is>
+          <t>add admob ads, ump consent and remove-ads purchase (off by default)</t>
+        </is>
+      </c>
+      <c r="D7" s="13" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t>25aeb89</t>
+        </is>
+      </c>
+      <c r="B8" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="C8" s="13" t="inlineStr">
+        <is>
+          <t>group app dependencies with comments</t>
+        </is>
+      </c>
+      <c r="D8" s="13" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>3710582</t>
+        </is>
+      </c>
+      <c r="B9" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="C9" s="13" t="inlineStr">
+        <is>
+          <t>add AI scan layer: worker client, app check, image pipeline, history</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="inlineStr">
+        <is>
+          <t>Giai đoạn A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="13" t="inlineStr">
+        <is>
           <t>(chưa commit)</t>
         </is>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B10" s="13" t="inlineStr">
         <is>
           <t>2026-10-26</t>
         </is>
       </c>
-      <c r="C7" s="13" t="inlineStr">
-        <is>
-          <t>AdMob + UMP + Billing "Gỡ quảng cáo"</t>
-        </is>
-      </c>
-      <c r="D7" s="13" t="inlineStr">
-        <is>
-          <t>Mặc định tắt (ads.enabled=false).</t>
+      <c r="C10" s="13" t="inlineStr">
+        <is>
+          <t>Phiên ẩn danh + Cloudflare Worker (giai đoạn B)</t>
+        </is>
+      </c>
+      <c r="D10" s="13" t="inlineStr">
+        <is>
+          <t>Worker chưa deploy.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D7"/>
+  <autoFilter ref="A1:D10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1574,7 +2054,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D62"/>
+  <dimension ref="A1:D81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1645,7 +2125,7 @@
       </c>
       <c r="D3" s="13" t="inlineStr">
         <is>
-          <t>System splash (giữ tới khi đọc xong theme + phiên), edge-to-edge, nhận deep link khi app đang mở, gắn InAppUpdateHandler + MonetizationInitializer.</t>
+          <t>System splash (giữ tới khi phiên sẵn sàng), edge-to-edge, nhận deep link khi app đang mở, gắn InAppUpdateHandler + MonetizationInitializer.</t>
         </is>
       </c>
     </row>
@@ -1667,7 +2147,7 @@
       </c>
       <c r="D4" s="13" t="inlineStr">
         <is>
-          <t>Theme + trạng thái đăng nhập toàn app (null = chưa đọc xong); ghi nhận lần mở app cho ReviewPolicy.</t>
+          <t>Theme + AuthState toàn app; tạo phiên ẩn danh khi mở app (sessionReady); ghi nhận lần mở app cho ReviewPolicy.</t>
         </is>
       </c>
     </row>
@@ -2503,7 +2983,7 @@
       </c>
       <c r="D42" s="13" t="inlineStr">
         <is>
-          <t>Backend Firebase Auth (mặc định); map lỗi Firebase sang AppError.</t>
+          <t>Backend Firebase Auth (mặc định): signInAnonymously, linkWithCredential khi tạo tài khoản; map lỗi Firebase sang AppError.</t>
         </is>
       </c>
     </row>
@@ -2525,7 +3005,7 @@
       </c>
       <c r="D43" s="13" t="inlineStr">
         <is>
-          <t>Backend REST riêng; đổi 1 dòng trong AppModule để dùng.</t>
+          <t>Backend REST riêng; đổi 1 dòng trong AppModule. Không hỗ trợ ẩn danh; AI cần Firebase Auth.</t>
         </is>
       </c>
     </row>
@@ -2547,7 +3027,7 @@
       </c>
       <c r="D44" s="13" t="inlineStr">
         <is>
-          <t>Đăng nhập/đăng ký/refresh/đăng xuất; lưu phiên + cache user.</t>
+          <t>ensureSession (phiên ẩn danh), đăng nhập, đăng ký = nâng cấp ẩn danh (giữ uid), refresh, đăng xuất → phiên ẩn danh mới; đổi uid thì xoá dữ liệu cục bộ.</t>
         </is>
       </c>
     </row>
@@ -2569,7 +3049,7 @@
       </c>
       <c r="D45" s="13" t="inlineStr">
         <is>
-          <t>Đăng nhập giả lập cho flavor mock.</t>
+          <t>Auth giả lập cho flavor mock: phiên ẩn danh demo-anon, nâng cấp giữ uid.</t>
         </is>
       </c>
     </row>
@@ -2591,7 +3071,7 @@
       </c>
       <c r="D46" s="13" t="inlineStr">
         <is>
-          <t>Refresh thất bại: đăng xuất, trừ khi chỉ là mất mạng.</t>
+          <t>Refresh bị từ chối: đăng xuất rồi tạo phiên ẩn danh mới; mất mạng thì giữ phiên.</t>
         </is>
       </c>
     </row>
@@ -2767,7 +3247,7 @@
       </c>
       <c r="D54" s="13" t="inlineStr">
         <is>
-          <t>3 tab Home/Explore/Settings; banner, xen kẽ demo, theme, thông báo, đánh giá, đăng xuất.</t>
+          <t>3 tab Home / Quét AI / Settings; banner, xen kẽ demo, theme, thông báo, đánh giá, Đăng nhập/Tạo tài khoản hoặc Đăng xuất.</t>
         </is>
       </c>
     </row>
@@ -2811,7 +3291,7 @@
       </c>
       <c r="D56" s="12" t="inlineStr">
         <is>
-          <t>NavHost + auth gate (hết phiên → về Login); Splash điều hướng theo trạng thái đăng nhập.</t>
+          <t>NavHost; Splash vào thẳng Home khi phiên sẵn sàng; account gate: người ẩn danh mở màn cần tài khoản → Login.</t>
         </is>
       </c>
     </row>
@@ -2833,7 +3313,7 @@
       </c>
       <c r="D57" s="13" t="inlineStr">
         <is>
-          <t>Route type-safe; requiresAuth() khai báo route công khai.</t>
+          <t>Route type-safe; accountRoutes khai báo màn cần tài khoản thật.</t>
         </is>
       </c>
     </row>
@@ -2947,8 +3427,426 @@
         </is>
       </c>
     </row>
+    <row r="63">
+      <c r="A63" s="11" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="B63" s="12" t="inlineStr">
+        <is>
+          <t>core/ai</t>
+        </is>
+      </c>
+      <c r="C63" s="12" t="inlineStr">
+        <is>
+          <t>AiClient.kt + AiModels.kt + AiApi.kt</t>
+        </is>
+      </c>
+      <c r="D63" s="12" t="inlineStr">
+        <is>
+          <t>run(task, input, serializer) → kết quả có kiểu + quota; hợp đồng API v1 với Worker.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="13" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="B64" s="13" t="inlineStr">
+        <is>
+          <t>core/ai</t>
+        </is>
+      </c>
+      <c r="C64" s="13" t="inlineStr">
+        <is>
+          <t>WorkerAiClient.kt</t>
+        </is>
+      </c>
+      <c r="D64" s="13" t="inlineStr">
+        <is>
+          <t>Gọi Worker; map 429 → QuotaExceeded, content_blocked → ContentBlocked, 403 app_check_failed → AppNotVerified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="13" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="B65" s="13" t="inlineStr">
+        <is>
+          <t>core/ai</t>
+        </is>
+      </c>
+      <c r="C65" s="13" t="inlineStr">
+        <is>
+          <t>FakeAiClient.kt</t>
+        </is>
+      </c>
+      <c r="D65" s="13" t="inlineStr">
+        <is>
+          <t>Flavor mock: kết quả mẫu theo task, quota giả lập 5 lượt/ngày, chạy offline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="13" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="B66" s="13" t="inlineStr">
+        <is>
+          <t>core/ai</t>
+        </is>
+      </c>
+      <c r="C66" s="13" t="inlineStr">
+        <is>
+          <t>AiSessionGuard.kt</t>
+        </is>
+      </c>
+      <c r="D66" s="13" t="inlineStr">
+        <is>
+          <t>Đảm bảo có phiên (ẩn danh) trước mỗi lần gọi AI.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="13" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="B67" s="13" t="inlineStr">
+        <is>
+          <t>core/image</t>
+        </is>
+      </c>
+      <c r="C67" s="13" t="inlineStr">
+        <is>
+          <t>ImagePicker.kt</t>
+        </is>
+      </c>
+      <c r="D67" s="13" t="inlineStr">
+        <is>
+          <t>rememberImagePicker: Photo Picker + camera hệ thống, không xin quyền.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="13" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="B68" s="13" t="inlineStr">
+        <is>
+          <t>core/image</t>
+        </is>
+      </c>
+      <c r="C68" s="13" t="inlineStr">
+        <is>
+          <t>ImagePreprocessor.kt + ImageSizing.kt</t>
+        </is>
+      </c>
+      <c r="D68" s="13" t="inlineStr">
+        <is>
+          <t>Xoay theo EXIF, thu về cạnh 1024px, JPEG 85, xoá EXIF/GPS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="13" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="B69" s="13" t="inlineStr">
+        <is>
+          <t>core/firebase</t>
+        </is>
+      </c>
+      <c r="C69" s="13" t="inlineStr">
+        <is>
+          <t>AppCheckProviders.kt (src/debug, src/release) + FirebaseAppCheckTokenProvider.kt</t>
+        </is>
+      </c>
+      <c r="D69" s="13" t="inlineStr">
+        <is>
+          <t>App Check: debug provider ở debug, Play Integrity ở release; lấy token cho interceptor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="13" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="B70" s="13" t="inlineStr">
+        <is>
+          <t>core/network</t>
+        </is>
+      </c>
+      <c r="C70" s="13" t="inlineStr">
+        <is>
+          <t>AppCheckInterceptor.kt</t>
+        </is>
+      </c>
+      <c r="D70" s="13" t="inlineStr">
+        <is>
+          <t>Gắn header X-Firebase-AppCheck vào request tới backend.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="13" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="B71" s="13" t="inlineStr">
+        <is>
+          <t>core/di</t>
+        </is>
+      </c>
+      <c r="C71" s="13" t="inlineStr">
+        <is>
+          <t>AiModule.kt</t>
+        </is>
+      </c>
+      <c r="D71" s="13" t="inlineStr">
+        <is>
+          <t>Koin: AiClient (fake/Worker), AiApi (timeout 60s), ImagePreprocessor, lịch sử AI, ScanViewModel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="11" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
+      <c r="B72" s="12" t="inlineStr">
+        <is>
+          <t>data/local</t>
+        </is>
+      </c>
+      <c r="C72" s="12" t="inlineStr">
+        <is>
+          <t>AiHistoryDao.kt, AiHistoryEntity.kt</t>
+        </is>
+      </c>
+      <c r="D72" s="12" t="inlineStr">
+        <is>
+          <t>Bảng ai_history (Room v2, AutoMigration).</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="13" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
+      <c r="B73" s="13" t="inlineStr">
+        <is>
+          <t>data/repository</t>
+        </is>
+      </c>
+      <c r="C73" s="13" t="inlineStr">
+        <is>
+          <t>AiHistoryRepository.kt</t>
+        </is>
+      </c>
+      <c r="D73" s="13" t="inlineStr">
+        <is>
+          <t>Lưu kết quả AI + ảnh thu nhỏ; xoá khi đăng xuất/đổi tài khoản.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="11" t="inlineStr">
+        <is>
+          <t>Domain</t>
+        </is>
+      </c>
+      <c r="B74" s="12" t="inlineStr">
+        <is>
+          <t>domain/model</t>
+        </is>
+      </c>
+      <c r="C74" s="12" t="inlineStr">
+        <is>
+          <t>AuthState.kt</t>
+        </is>
+      </c>
+      <c r="D74" s="12" t="inlineStr">
+        <is>
+          <t>SignedOut / Anonymous / SignedIn.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="11" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="B75" s="12" t="inlineStr">
+        <is>
+          <t>feature/scan</t>
+        </is>
+      </c>
+      <c r="C75" s="12" t="inlineStr">
+        <is>
+          <t>ScanScreen.kt + ScanViewModel.kt + DemoScan.kt</t>
+        </is>
+      </c>
+      <c r="D75" s="12" t="inlineStr">
+        <is>
+          <t>Màn demo Quét AI: chụp/chọn ảnh → kết quả, độ tin cậy, lời khuyên, báo cáo, lịch sử.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="11" t="inlineStr">
+        <is>
+          <t>Worker</t>
+        </is>
+      </c>
+      <c r="B76" s="12" t="inlineStr">
+        <is>
+          <t>worker/src</t>
+        </is>
+      </c>
+      <c r="C76" s="12" t="inlineStr">
+        <is>
+          <t>index.ts</t>
+        </is>
+      </c>
+      <c r="D76" s="12" t="inlineStr">
+        <is>
+          <t>Router /health, /v1/run, /v1/report; luồng run: xác thực → task → quota → Gemini → kiểm tra schema.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="13" t="inlineStr">
+        <is>
+          <t>Worker</t>
+        </is>
+      </c>
+      <c r="B77" s="13" t="inlineStr">
+        <is>
+          <t>worker/src/auth</t>
+        </is>
+      </c>
+      <c r="C77" s="13" t="inlineStr">
+        <is>
+          <t>tokens.ts</t>
+        </is>
+      </c>
+      <c r="D77" s="13" t="inlineStr">
+        <is>
+          <t>Xác minh App Check (403) rồi Firebase ID token (401) bằng jose + JWKS của Google.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="13" t="inlineStr">
+        <is>
+          <t>Worker</t>
+        </is>
+      </c>
+      <c r="B78" s="13" t="inlineStr">
+        <is>
+          <t>worker/src/quota</t>
+        </is>
+      </c>
+      <c r="C78" s="13" t="inlineStr">
+        <is>
+          <t>QuotaCounter.ts + day.ts</t>
+        </is>
+      </c>
+      <c r="D78" s="13" t="inlineStr">
+        <is>
+          <t>Durable Object đếm lượt mỗi uid/ngày (0h giờ VN), consume/refund.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="13" t="inlineStr">
+        <is>
+          <t>Worker</t>
+        </is>
+      </c>
+      <c r="B79" s="13" t="inlineStr">
+        <is>
+          <t>worker/src/tasks</t>
+        </is>
+      </c>
+      <c r="C79" s="13" t="inlineStr">
+        <is>
+          <t>identify_object.ts + index.ts + types.ts</t>
+        </is>
+      </c>
+      <c r="D79" s="13" t="inlineStr">
+        <is>
+          <t>Task AI: model, prompt, JSON schema, số lượt; ENABLED_TASKS bật theo deployment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="13" t="inlineStr">
+        <is>
+          <t>Worker</t>
+        </is>
+      </c>
+      <c r="B80" s="13" t="inlineStr">
+        <is>
+          <t>worker/src</t>
+        </is>
+      </c>
+      <c r="C80" s="13" t="inlineStr">
+        <is>
+          <t>gemini.ts + validate.ts</t>
+        </is>
+      </c>
+      <c r="D80" s="13" t="inlineStr">
+        <is>
+          <t>Gọi generateContent (JSON mode), nhận diện bị chặn; kiểm tra request và kết quả theo schema.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="13" t="inlineStr">
+        <is>
+          <t>Worker</t>
+        </is>
+      </c>
+      <c r="B81" s="13" t="inlineStr">
+        <is>
+          <t>worker</t>
+        </is>
+      </c>
+      <c r="C81" s="13" t="inlineStr">
+        <is>
+          <t>wrangler.jsonc + migrations/</t>
+        </is>
+      </c>
+      <c r="D81" s="13" t="inlineStr">
+        <is>
+          <t>Env dev/prod, binding Durable Object + D1 (bảng reports), biến cấu hình.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D62"/>
+  <autoFilter ref="A1:D81"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2959,7 +3857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E34"/>
+  <dimension ref="A1:E42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3815,8 +4713,212 @@
       </c>
       <c r="E34" s="13" t="inlineStr"/>
     </row>
+    <row r="35">
+      <c r="A35" s="11" t="inlineStr">
+        <is>
+          <t>Firebase</t>
+        </is>
+      </c>
+      <c r="B35" s="12" t="inlineStr">
+        <is>
+          <t>Firebase App Check (Play Integrity / debug)</t>
+        </is>
+      </c>
+      <c r="C35" s="12" t="inlineStr">
+        <is>
+          <t>19.4.1 (theo BOM)</t>
+        </is>
+      </c>
+      <c r="D35" s="12" t="inlineStr">
+        <is>
+          <t>Xác minh request đến từ app thật</t>
+        </is>
+      </c>
+      <c r="E35" s="12" t="inlineStr">
+        <is>
+          <t>Debug provider chỉ có ở bản debug.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="11" t="inlineStr">
+        <is>
+          <t>Dữ liệu</t>
+        </is>
+      </c>
+      <c r="B36" s="12" t="inlineStr">
+        <is>
+          <t>ExifInterface</t>
+        </is>
+      </c>
+      <c r="C36" s="12" t="inlineStr">
+        <is>
+          <t>1.4.2</t>
+        </is>
+      </c>
+      <c r="D36" s="12" t="inlineStr">
+        <is>
+          <t>Đọc hướng xoay ảnh</t>
+        </is>
+      </c>
+      <c r="E36" s="12" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="11" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="B37" s="12" t="inlineStr">
+        <is>
+          <t>Gemini API (generateContent)</t>
+        </is>
+      </c>
+      <c r="C37" s="12" t="inlineStr">
+        <is>
+          <t>gemini-3.5-flash-lite</t>
+        </is>
+      </c>
+      <c r="D37" s="12" t="inlineStr">
+        <is>
+          <t>Nhận diện ảnh, trả JSON theo schema</t>
+        </is>
+      </c>
+      <c r="E37" s="12" t="inlineStr">
+        <is>
+          <t>Gọi từ Worker; model đổi theo từng task.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="11" t="inlineStr">
+        <is>
+          <t>Worker</t>
+        </is>
+      </c>
+      <c r="B38" s="12" t="inlineStr">
+        <is>
+          <t>Wrangler</t>
+        </is>
+      </c>
+      <c r="C38" s="12" t="inlineStr">
+        <is>
+          <t>4.152.0</t>
+        </is>
+      </c>
+      <c r="D38" s="12" t="inlineStr">
+        <is>
+          <t>Chạy/deploy Cloudflare Worker</t>
+        </is>
+      </c>
+      <c r="E38" s="12" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="13" t="inlineStr">
+        <is>
+          <t>Worker</t>
+        </is>
+      </c>
+      <c r="B39" s="13" t="inlineStr">
+        <is>
+          <t>jose</t>
+        </is>
+      </c>
+      <c r="C39" s="13" t="inlineStr">
+        <is>
+          <t>6.2.13</t>
+        </is>
+      </c>
+      <c r="D39" s="13" t="inlineStr">
+        <is>
+          <t>Xác minh JWT (ID token, App Check)</t>
+        </is>
+      </c>
+      <c r="E39" s="13" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="13" t="inlineStr">
+        <is>
+          <t>Worker</t>
+        </is>
+      </c>
+      <c r="B40" s="13" t="inlineStr">
+        <is>
+          <t>@cfworker/json-schema</t>
+        </is>
+      </c>
+      <c r="C40" s="13" t="inlineStr">
+        <is>
+          <t>4.1.1</t>
+        </is>
+      </c>
+      <c r="D40" s="13" t="inlineStr">
+        <is>
+          <t>Kiểm tra kết quả AI theo schema</t>
+        </is>
+      </c>
+      <c r="E40" s="13" t="inlineStr">
+        <is>
+          <t>ajv không chạy được trên Workers (dùng eval).</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="13" t="inlineStr">
+        <is>
+          <t>Worker</t>
+        </is>
+      </c>
+      <c r="B41" s="13" t="inlineStr">
+        <is>
+          <t>@cloudflare/vitest-plugin + Vitest</t>
+        </is>
+      </c>
+      <c r="C41" s="13" t="inlineStr">
+        <is>
+          <t>1.4.7 + 5.0.5</t>
+        </is>
+      </c>
+      <c r="D41" s="13" t="inlineStr">
+        <is>
+          <t>Test chạy trong workerd</t>
+        </is>
+      </c>
+      <c r="E41" s="13" t="inlineStr">
+        <is>
+          <t>Thay cho vitest-pool-workers (đã ngừng).</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="13" t="inlineStr">
+        <is>
+          <t>Worker</t>
+        </is>
+      </c>
+      <c r="B42" s="13" t="inlineStr">
+        <is>
+          <t>TypeScript</t>
+        </is>
+      </c>
+      <c r="C42" s="13" t="inlineStr">
+        <is>
+          <t>5.9.3</t>
+        </is>
+      </c>
+      <c r="D42" s="13" t="inlineStr">
+        <is>
+          <t>Ngôn ngữ Worker</t>
+        </is>
+      </c>
+      <c r="E42" s="13" t="inlineStr">
+        <is>
+          <t>Chưa dùng TS 7.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E34"/>
+  <autoFilter ref="A1:E42"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3827,7 +4929,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -3889,7 +4991,7 @@
       </c>
       <c r="C3" s="13" t="inlineStr">
         <is>
-          <t>MainActivity: giữ system splash tới khi MainViewModel đọc xong theme + trạng thái đăng nhập.</t>
+          <t>MainViewModel.ensureSession(): chưa có phiên thì tạo phiên ẩn danh; system splash giữ tới khi xong (offline vẫn vào app).</t>
         </is>
       </c>
       <c r="D3" s="13" t="inlineStr">
@@ -3909,7 +5011,7 @@
       </c>
       <c r="C4" s="13" t="inlineStr">
         <is>
-          <t>SplashRoute (không hiển thị) điều hướng sang Home hoặc Login.</t>
+          <t>SplashRoute (không hiển thị) vào thẳng Home.</t>
         </is>
       </c>
       <c r="D4" s="13" t="inlineStr">
@@ -3949,7 +5051,7 @@
       </c>
       <c r="C6" s="12" t="inlineStr">
         <is>
-          <t>LoginViewModel.submit → LoginUseCase validate (email, mật khẩu ≥ 6).</t>
+          <t>Từ Cài đặt mở Login (người dùng đang ẩn danh). LoginViewModel.submit → LoginUseCase validate (email, mật khẩu ≥ 6).</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
@@ -4009,12 +5111,12 @@
       </c>
       <c r="C9" s="13" t="inlineStr">
         <is>
-          <t>Gửi LoginEvent.Authenticated → màn Login điều hướng sang Home.</t>
+          <t>Tạo tài khoản = nâng cấp phiên ẩn danh (giữ uid); đăng nhập tài khoản khác thì xoá dữ liệu cục bộ. Xong quay về Home.</t>
         </is>
       </c>
       <c r="D9" s="13" t="inlineStr">
         <is>
-          <t>LoginScreen.kt</t>
+          <t>AuthRepositoryImpl.kt, AppNavHost.kt</t>
         </is>
       </c>
     </row>
@@ -4101,12 +5203,12 @@
       </c>
       <c r="C14" s="12" t="inlineStr">
         <is>
-          <t>Phiên bị xoá (đăng xuất hoặc refresh thất bại) → isAuthenticated = false.</t>
+          <t>Đăng xuất hoặc refresh bị từ chối → xoá phiên, user cache, lịch sử AI.</t>
         </is>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
-          <t>AppDataStore.kt</t>
+          <t>AuthRepositoryImpl.kt</t>
         </is>
       </c>
     </row>
@@ -4121,12 +5223,12 @@
       </c>
       <c r="C15" s="13" t="inlineStr">
         <is>
-          <t>Auth gate trong AppNavHost: đang ở màn cần đăng nhập thì về Login, xoá back stack.</t>
+          <t>Tạo ngay phiên ẩn danh mới; người dùng ở lại Home. Màn trong accountRoutes thì chuyển sang Login.</t>
         </is>
       </c>
       <c r="D15" s="13" t="inlineStr">
         <is>
-          <t>AppNavHost.kt, AppRoutes.kt</t>
+          <t>AuthRepositoryImpl.kt, AppNavHost.kt</t>
         </is>
       </c>
     </row>
@@ -4450,8 +5552,88 @@
         </is>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" s="11" t="inlineStr">
+        <is>
+          <t>Quét AI</t>
+        </is>
+      </c>
+      <c r="B32" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C32" s="12" t="inlineStr">
+        <is>
+          <t>Chụp/chọn ảnh (không xin quyền) → ImagePreprocessor nén, xoay, xoá EXIF.</t>
+        </is>
+      </c>
+      <c r="D32" s="12" t="inlineStr">
+        <is>
+          <t>ImagePicker.kt, ImagePreprocessor.kt</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="13" t="inlineStr">
+        <is>
+          <t>Quét AI</t>
+        </is>
+      </c>
+      <c r="B33" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="C33" s="13" t="inlineStr">
+        <is>
+          <t>AiSessionGuard đảm bảo có phiên → WorkerAiClient gửi task + ảnh base64, kèm ID token + App Check.</t>
+        </is>
+      </c>
+      <c r="D33" s="13" t="inlineStr">
+        <is>
+          <t>WorkerAiClient.kt</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="13" t="inlineStr">
+        <is>
+          <t>Quét AI</t>
+        </is>
+      </c>
+      <c r="B34" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="C34" s="13" t="inlineStr">
+        <is>
+          <t>Worker: App Check → ID token → task → quota → Gemini → kiểm tra schema → trả result + quota.</t>
+        </is>
+      </c>
+      <c r="D34" s="13" t="inlineStr">
+        <is>
+          <t>worker/src/index.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="13" t="inlineStr">
+        <is>
+          <t>Quét AI</t>
+        </is>
+      </c>
+      <c r="B35" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="C35" s="13" t="inlineStr">
+        <is>
+          <t>App hiển thị kết quả, lưu lịch sử; nút Báo cáo → /v1/report → D1.</t>
+        </is>
+      </c>
+      <c r="D35" s="13" t="inlineStr">
+        <is>
+          <t>ScanViewModel.kt, AiHistoryRepository.kt</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D31"/>
+  <autoFilter ref="A1:D35"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4462,7 +5644,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -4537,17 +5719,17 @@
     <row r="5">
       <c r="A5" s="13" t="inlineStr">
         <is>
-          <t>Thêm route công khai</t>
+          <t>Thêm màn cần tài khoản</t>
         </is>
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>Khai báo route @Serializable trong AppRoutes; nếu không cần đăng nhập thì thêm vào requiresAuth().</t>
+          <t>Khai báo route @Serializable trong AppRoutes; thêm vào accountRoutes nếu cần tài khoản thật (không ẩn danh).</t>
         </is>
       </c>
       <c r="C5" s="13" t="inlineStr">
         <is>
-          <t>Mặc định mọi route đều cần đăng nhập.</t>
+          <t>Mặc định mọi màn dùng được với phiên ẩn danh.</t>
         </is>
       </c>
     </row>
@@ -4713,8 +5895,55 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" s="13" t="inlineStr">
+        <is>
+          <t>Thêm task AI mới</t>
+        </is>
+      </c>
+      <c r="B16" s="13" t="inlineStr">
+        <is>
+          <t>Worker: file task (prompt, schema, model, cost) + đăng ký + ENABLED_TASKS. App: data class @Serializable khớp schema, mẫu JSON cho FakeAiClient, gọi aiClient.run(...).</t>
+        </is>
+      </c>
+      <c r="C16" s="13" t="inlineStr">
+        <is>
+          <t>Prompt luôn phải có nhánh "không nhận diện được".</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="13" t="inlineStr">
+        <is>
+          <t>Nối app với Worker</t>
+        </is>
+      </c>
+      <c r="B17" s="13" t="inlineStr">
+        <is>
+          <t>Deploy Worker (worker/README.md) → đặt ai.workerUrl.dev / ai.workerUrl.prod trong gradle.properties → chạy devDebug.</t>
+        </is>
+      </c>
+      <c r="C17" s="13" t="inlineStr">
+        <is>
+          <t>Đăng ký debug token App Check từ logcat.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="13" t="inlineStr">
+        <is>
+          <t>Xem báo cáo AI</t>
+        </is>
+      </c>
+      <c r="B18" s="13" t="inlineStr">
+        <is>
+          <t>npx wrangler d1 execute &lt;db&gt; --env &lt;env&gt; --remote --command "SELECT * FROM reports ORDER BY id DESC LIMIT 20"</t>
+        </is>
+      </c>
+      <c r="C18" s="13" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:C15"/>
+  <autoFilter ref="A1:C18"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4725,7 +5954,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5196,8 +6425,140 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" s="11" t="inlineStr">
+        <is>
+          <t>BuildConfig</t>
+        </is>
+      </c>
+      <c r="B22" s="12" t="inlineStr">
+        <is>
+          <t>USE_FAKE_AI</t>
+        </is>
+      </c>
+      <c r="C22" s="12" t="inlineStr">
+        <is>
+          <t>productFlavors</t>
+        </is>
+      </c>
+      <c r="D22" s="12" t="inlineStr">
+        <is>
+          <t>true ở mock (FakeAiClient).</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="13" t="inlineStr">
+        <is>
+          <t>BuildConfig</t>
+        </is>
+      </c>
+      <c r="B23" s="13" t="inlineStr">
+        <is>
+          <t>AI_BASE_URL</t>
+        </is>
+      </c>
+      <c r="C23" s="13" t="inlineStr">
+        <is>
+          <t>gradle.properties: ai.workerUrl.dev / ai.workerUrl.prod (fallback ai.workerUrl)</t>
+        </is>
+      </c>
+      <c r="D23" s="13" t="inlineStr">
+        <is>
+          <t>URL Worker theo flavor, kết thúc bằng /.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="11" t="inlineStr">
+        <is>
+          <t>Worker var</t>
+        </is>
+      </c>
+      <c r="B24" s="12" t="inlineStr">
+        <is>
+          <t>FIREBASE_PROJECT_ID / FIREBASE_PROJECT_NUMBER / ALLOWED_APP_IDS</t>
+        </is>
+      </c>
+      <c r="C24" s="12" t="inlineStr">
+        <is>
+          <t>worker/wrangler.jsonc (mỗi env)</t>
+        </is>
+      </c>
+      <c r="D24" s="12" t="inlineStr">
+        <is>
+          <t>Dùng để xác minh token.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="13" t="inlineStr">
+        <is>
+          <t>Worker var</t>
+        </is>
+      </c>
+      <c r="B25" s="13" t="inlineStr">
+        <is>
+          <t>APP_CHECK_MODE</t>
+        </is>
+      </c>
+      <c r="C25" s="13" t="inlineStr">
+        <is>
+          <t>worker/wrangler.jsonc</t>
+        </is>
+      </c>
+      <c r="D25" s="13" t="inlineStr">
+        <is>
+          <t>monitor (chỉ ghi log, dùng lúc tích hợp) hoặc enforce.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="13" t="inlineStr">
+        <is>
+          <t>Worker var</t>
+        </is>
+      </c>
+      <c r="B26" s="13" t="inlineStr">
+        <is>
+          <t>ENABLED_TASKS, DAILY_LIMIT, REPORT_DAILY_LIMIT, QUOTA_UTC_OFFSET_MINUTES</t>
+        </is>
+      </c>
+      <c r="C26" s="13" t="inlineStr">
+        <is>
+          <t>worker/wrangler.jsonc</t>
+        </is>
+      </c>
+      <c r="D26" s="13" t="inlineStr">
+        <is>
+          <t>Task bật, lượt/ngày, báo cáo/ngày, múi giờ (420 = VN).</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="11" t="inlineStr">
+        <is>
+          <t>Worker secret</t>
+        </is>
+      </c>
+      <c r="B27" s="12" t="inlineStr">
+        <is>
+          <t>GEMINI_API_KEY</t>
+        </is>
+      </c>
+      <c r="C27" s="12" t="inlineStr">
+        <is>
+          <t>npx wrangler secret put GEMINI_API_KEY --env &lt;env&gt;</t>
+        </is>
+      </c>
+      <c r="D27" s="12" t="inlineStr">
+        <is>
+          <t>Không bao giờ nằm trong app.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D21"/>
+  <autoFilter ref="A1:D27"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5208,186 +6569,388 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="70" customWidth="1" min="1" max="1"/>
-    <col width="44" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="52" customWidth="1" min="3" max="3"/>
+    <col width="46" customWidth="1" min="4" max="4"/>
+    <col width="52" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="10" t="inlineStr">
         <is>
-          <t>Lệnh</t>
+          <t>Loại</t>
         </is>
       </c>
       <c r="B1" s="10" t="inlineStr">
         <is>
-          <t>Mục đích</t>
+          <t>Endpoint / mã</t>
         </is>
       </c>
       <c r="C1" s="10" t="inlineStr">
         <is>
-          <t>Khi nào dùng</t>
+          <t>Khi nào / request</t>
+        </is>
+      </c>
+      <c r="D1" s="10" t="inlineStr">
+        <is>
+          <t>Response / app xử lý thành</t>
+        </is>
+      </c>
+      <c r="E1" s="10" t="inlineStr">
+        <is>
+          <t>Ghi chú</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr">
-        <is>
-          <t>./gradlew assembleMockDebug</t>
-        </is>
-      </c>
-      <c r="B2" s="13" t="inlineStr">
-        <is>
-          <t>Build APK demo (đăng nhập giả lập)</t>
-        </is>
-      </c>
-      <c r="C2" s="13" t="inlineStr">
-        <is>
-          <t>Chạy thử nhanh</t>
+      <c r="A2" s="11" t="inlineStr">
+        <is>
+          <t>Endpoint</t>
+        </is>
+      </c>
+      <c r="B2" s="12" t="inlineStr">
+        <is>
+          <t>GET /health</t>
+        </is>
+      </c>
+      <c r="C2" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D2" s="12" t="inlineStr">
+        <is>
+          <t>200 {"ok": true}</t>
+        </is>
+      </c>
+      <c r="E2" s="12" t="inlineStr">
+        <is>
+          <t>Kiểm tra Worker còn sống.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="13" t="inlineStr">
         <is>
-          <t>./gradlew assembleDevDebug</t>
+          <t>Endpoint</t>
         </is>
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>Build APK với backend thật</t>
+          <t>POST /v1/run</t>
         </is>
       </c>
       <c r="C3" s="13" t="inlineStr">
         <is>
-          <t>Test Firebase/API thật</t>
+          <t>{ task, locale, text?, images: [{ mimeType, data (base64) }] }</t>
+        </is>
+      </c>
+      <c r="D3" s="13" t="inlineStr">
+        <is>
+          <t>200 { result, quota: { remaining, limit, resetAt } }</t>
+        </is>
+      </c>
+      <c r="E3" s="13" t="inlineStr">
+        <is>
+          <t>Header: Authorization: Bearer &lt;Firebase ID token&gt;, X-Firebase-AppCheck.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="13" t="inlineStr">
         <is>
-          <t>./gradlew testMockDebugUnitTest</t>
+          <t>Endpoint</t>
         </is>
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>Chạy toàn bộ unit test (gồm Robolectric)</t>
+          <t>POST /v1/report</t>
         </is>
       </c>
       <c r="C4" s="13" t="inlineStr">
         <is>
-          <t>Trước mỗi commit</t>
+          <t>{ task, result, reason }</t>
+        </is>
+      </c>
+      <c r="D4" s="13" t="inlineStr">
+        <is>
+          <t>204</t>
+        </is>
+      </c>
+      <c r="E4" s="13" t="inlineStr">
+        <is>
+          <t>Ghi bảng reports trong D1; tối đa REPORT_DAILY_LIMIT/ngày.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
-        <is>
-          <t>./gradlew ktlintFormat</t>
-        </is>
-      </c>
-      <c r="B5" s="13" t="inlineStr">
-        <is>
-          <t>Tự sửa format</t>
-        </is>
-      </c>
-      <c r="C5" s="13" t="inlineStr">
-        <is>
-          <t>Trước khi commit</t>
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>Lỗi</t>
+        </is>
+      </c>
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>400 invalid_request</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
+          <t>Body sai, sai số ảnh, mime không phải jpeg/png/webp, base64 sai</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="inlineStr">
+        <is>
+          <t>AppError.Server</t>
+        </is>
+      </c>
+      <c r="E5" s="12" t="inlineStr">
+        <is>
+          <t>Lỗi lập trình phía app.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="13" t="inlineStr">
         <is>
-          <t>./gradlew ktlintCheck detekt</t>
+          <t>Lỗi</t>
         </is>
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>Kiểm tra format + code smell</t>
+          <t>401 unauthorized</t>
         </is>
       </c>
       <c r="C6" s="13" t="inlineStr">
         <is>
-          <t>CI chạy; lỗi là fail</t>
+          <t>ID token thiếu/hết hạn/sai project</t>
+        </is>
+      </c>
+      <c r="D6" s="13" t="inlineStr">
+        <is>
+          <t>TokenAuthenticator refresh rồi gửi lại 1 lần</t>
+        </is>
+      </c>
+      <c r="E6" s="13" t="inlineStr">
+        <is>
+          <t>Refresh bị từ chối → phiên ẩn danh mới.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="13" t="inlineStr">
         <is>
-          <t>./gradlew lintMockDebug</t>
+          <t>Lỗi</t>
         </is>
       </c>
       <c r="B7" s="13" t="inlineStr">
         <is>
-          <t>Android Lint (warning = error)</t>
+          <t>403 app_check_failed</t>
         </is>
       </c>
       <c r="C7" s="13" t="inlineStr">
         <is>
-          <t>CI chạy</t>
+          <t>App Check thiếu/sai app (chế độ enforce)</t>
+        </is>
+      </c>
+      <c r="D7" s="13" t="inlineStr">
+        <is>
+          <t>AppError.AppNotVerified</t>
+        </is>
+      </c>
+      <c r="E7" s="13" t="inlineStr">
+        <is>
+          <t>Debug: đăng ký debug token. Release: phải cài từ Google Play.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="13" t="inlineStr">
         <is>
-          <t>./gradlew bundleProdRelease -PversionCode=N -PversionName=X</t>
+          <t>Lỗi</t>
         </is>
       </c>
       <c r="B8" s="13" t="inlineStr">
         <is>
-          <t>Build AAB phát hành</t>
+          <t>404 unknown_task / not_found</t>
         </is>
       </c>
       <c r="C8" s="13" t="inlineStr">
         <is>
-          <t>Upload CH Play</t>
-        </is>
-      </c>
+          <t>Task không có trong ENABLED_TASKS, sai đường dẫn</t>
+        </is>
+      </c>
+      <c r="D8" s="13" t="inlineStr">
+        <is>
+          <t>AppError.Server</t>
+        </is>
+      </c>
+      <c r="E8" s="13" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="13" t="inlineStr">
         <is>
-          <t>./gradlew bundleProdRelease -Pads.enabled=true</t>
+          <t>Lỗi</t>
         </is>
       </c>
       <c r="B9" s="13" t="inlineStr">
         <is>
-          <t>Build thử với quảng cáo bật</t>
+          <t>405 method_not_allowed</t>
         </is>
       </c>
       <c r="C9" s="13" t="inlineStr">
         <is>
-          <t>Khi bật kiếm tiền</t>
-        </is>
-      </c>
+          <t>Sai phương thức HTTP</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="inlineStr">
+        <is>
+          <t>AppError.Server</t>
+        </is>
+      </c>
+      <c r="E9" s="13" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="13" t="inlineStr">
         <is>
-          <t>./gradlew ktlintCheck detekt lintMockDebug testMockDebugUnitTest testDevDebugUnitTest assembleMockDebug bundleProdRelease</t>
+          <t>Lỗi</t>
         </is>
       </c>
       <c r="B10" s="13" t="inlineStr">
         <is>
-          <t>Kiểm tra đầy đủ như CI</t>
+          <t>413 payload_too_large</t>
         </is>
       </c>
       <c r="C10" s="13" t="inlineStr">
         <is>
-          <t>Trước khi push</t>
+          <t>Body &gt; 4 MB hoặc ảnh &gt; 1,5 MB</t>
+        </is>
+      </c>
+      <c r="D10" s="13" t="inlineStr">
+        <is>
+          <t>AppError.Server</t>
+        </is>
+      </c>
+      <c r="E10" s="13" t="inlineStr">
+        <is>
+          <t>ImagePreprocessor đã nén về ~200 KB.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="13" t="inlineStr">
+        <is>
+          <t>Lỗi</t>
+        </is>
+      </c>
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>422 content_blocked</t>
+        </is>
+      </c>
+      <c r="C11" s="13" t="inlineStr">
+        <is>
+          <t>Gemini chặn vì an toàn</t>
+        </is>
+      </c>
+      <c r="D11" s="13" t="inlineStr">
+        <is>
+          <t>AppError.ContentBlocked</t>
+        </is>
+      </c>
+      <c r="E11" s="13" t="inlineStr">
+        <is>
+          <t>Vẫn tính lượt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="13" t="inlineStr">
+        <is>
+          <t>Lỗi</t>
+        </is>
+      </c>
+      <c r="B12" s="13" t="inlineStr">
+        <is>
+          <t>429 quota_exceeded (+ resetAt)</t>
+        </is>
+      </c>
+      <c r="C12" s="13" t="inlineStr">
+        <is>
+          <t>Hết lượt trong ngày (0h giờ VN đặt lại)</t>
+        </is>
+      </c>
+      <c r="D12" s="13" t="inlineStr">
+        <is>
+          <t>AppError.QuotaExceeded</t>
+        </is>
+      </c>
+      <c r="E12" s="13" t="inlineStr">
+        <is>
+          <t>Người dùng khác không bị ảnh hưởng.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="13" t="inlineStr">
+        <is>
+          <t>Lỗi</t>
+        </is>
+      </c>
+      <c r="B13" s="13" t="inlineStr">
+        <is>
+          <t>500 internal_error</t>
+        </is>
+      </c>
+      <c r="C13" s="13" t="inlineStr">
+        <is>
+          <t>Lỗi không lường trước (ví dụ không tải được khoá Google)</t>
+        </is>
+      </c>
+      <c r="D13" s="13" t="inlineStr">
+        <is>
+          <t>AppError.Server</t>
+        </is>
+      </c>
+      <c r="E13" s="13" t="inlineStr">
+        <is>
+          <t>Xem log: npx wrangler tail.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="13" t="inlineStr">
+        <is>
+          <t>Lỗi</t>
+        </is>
+      </c>
+      <c r="B14" s="13" t="inlineStr">
+        <is>
+          <t>502 upstream_error</t>
+        </is>
+      </c>
+      <c r="C14" s="13" t="inlineStr">
+        <is>
+          <t>Gemini lỗi/không truy cập được, hoặc trả JSON sai schema</t>
+        </is>
+      </c>
+      <c r="D14" s="13" t="inlineStr">
+        <is>
+          <t>AppError.Server</t>
+        </is>
+      </c>
+      <c r="E14" s="13" t="inlineStr">
+        <is>
+          <t>Hoàn lượt. Log gemini_error / schema_mismatch.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C10"/>
+  <autoFilter ref="A1:E14"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5398,7 +6961,265 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:C14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="70" customWidth="1" min="1" max="1"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="10" t="inlineStr">
+        <is>
+          <t>Lệnh</t>
+        </is>
+      </c>
+      <c r="B1" s="10" t="inlineStr">
+        <is>
+          <t>Mục đích</t>
+        </is>
+      </c>
+      <c r="C1" s="10" t="inlineStr">
+        <is>
+          <t>Khi nào dùng</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="13" t="inlineStr">
+        <is>
+          <t>./gradlew assembleMockDebug</t>
+        </is>
+      </c>
+      <c r="B2" s="13" t="inlineStr">
+        <is>
+          <t>Build APK demo (đăng nhập giả lập)</t>
+        </is>
+      </c>
+      <c r="C2" s="13" t="inlineStr">
+        <is>
+          <t>Chạy thử nhanh</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>./gradlew assembleDevDebug</t>
+        </is>
+      </c>
+      <c r="B3" s="13" t="inlineStr">
+        <is>
+          <t>Build APK với backend thật</t>
+        </is>
+      </c>
+      <c r="C3" s="13" t="inlineStr">
+        <is>
+          <t>Test Firebase/API thật</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="13" t="inlineStr">
+        <is>
+          <t>./gradlew testMockDebugUnitTest</t>
+        </is>
+      </c>
+      <c r="B4" s="13" t="inlineStr">
+        <is>
+          <t>Chạy toàn bộ unit test (gồm Robolectric)</t>
+        </is>
+      </c>
+      <c r="C4" s="13" t="inlineStr">
+        <is>
+          <t>Trước mỗi commit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>./gradlew ktlintFormat</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>Tự sửa format</t>
+        </is>
+      </c>
+      <c r="C5" s="13" t="inlineStr">
+        <is>
+          <t>Trước khi commit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="13" t="inlineStr">
+        <is>
+          <t>./gradlew ktlintCheck detekt</t>
+        </is>
+      </c>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>Kiểm tra format + code smell</t>
+        </is>
+      </c>
+      <c r="C6" s="13" t="inlineStr">
+        <is>
+          <t>CI chạy; lỗi là fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>./gradlew lintMockDebug</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>Android Lint (warning = error)</t>
+        </is>
+      </c>
+      <c r="C7" s="13" t="inlineStr">
+        <is>
+          <t>CI chạy</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t>./gradlew bundleProdRelease -PversionCode=N -PversionName=X</t>
+        </is>
+      </c>
+      <c r="B8" s="13" t="inlineStr">
+        <is>
+          <t>Build AAB phát hành</t>
+        </is>
+      </c>
+      <c r="C8" s="13" t="inlineStr">
+        <is>
+          <t>Upload CH Play</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>./gradlew bundleProdRelease -Pads.enabled=true</t>
+        </is>
+      </c>
+      <c r="B9" s="13" t="inlineStr">
+        <is>
+          <t>Build thử với quảng cáo bật</t>
+        </is>
+      </c>
+      <c r="C9" s="13" t="inlineStr">
+        <is>
+          <t>Khi bật kiếm tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="13" t="inlineStr">
+        <is>
+          <t>./gradlew ktlintCheck detekt lintMockDebug testMockDebugUnitTest testDevDebugUnitTest assembleMockDebug bundleProdRelease</t>
+        </is>
+      </c>
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>Kiểm tra đầy đủ như CI</t>
+        </is>
+      </c>
+      <c r="C10" s="13" t="inlineStr">
+        <is>
+          <t>Trước khi push</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="13" t="inlineStr">
+        <is>
+          <t>cd worker &amp;&amp; npm ci &amp;&amp; npm test</t>
+        </is>
+      </c>
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>Test Worker trong workerd</t>
+        </is>
+      </c>
+      <c r="C11" s="13" t="inlineStr">
+        <is>
+          <t>Trước khi deploy Worker</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="13" t="inlineStr">
+        <is>
+          <t>cd worker &amp;&amp; npm run dev</t>
+        </is>
+      </c>
+      <c r="B12" s="13" t="inlineStr">
+        <is>
+          <t>Chạy Worker trên máy (cần .dev.vars)</t>
+        </is>
+      </c>
+      <c r="C12" s="13" t="inlineStr">
+        <is>
+          <t>Thử nhanh</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="13" t="inlineStr">
+        <is>
+          <t>cd worker &amp;&amp; npm run deploy:dev / deploy:prod</t>
+        </is>
+      </c>
+      <c r="B13" s="13" t="inlineStr">
+        <is>
+          <t>Deploy Worker</t>
+        </is>
+      </c>
+      <c r="C13" s="13" t="inlineStr">
+        <is>
+          <t>Sau khi đổi prompt, task, cấu hình</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="13" t="inlineStr">
+        <is>
+          <t>cd worker &amp;&amp; npx wrangler tail --env dev</t>
+        </is>
+      </c>
+      <c r="B14" s="13" t="inlineStr">
+        <is>
+          <t>Xem log Worker trực tiếp</t>
+        </is>
+      </c>
+      <c r="C14" s="13" t="inlineStr">
+        <is>
+          <t>Gỡ lỗi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:C14"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -5532,7 +7353,7 @@
     <row r="7">
       <c r="A7" s="13" t="inlineStr">
         <is>
-          <t>TokenAuthenticatorTest</t>
+          <t>AppCheckInterceptorTest</t>
         </is>
       </c>
       <c r="B7" s="13" t="inlineStr">
@@ -5541,38 +7362,38 @@
         </is>
       </c>
       <c r="C7" s="13" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>Refresh 1 lần khi 401, không lặp vô hạn.</t>
+          <t>Gắn / không gắn header App Check.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="13" t="inlineStr">
         <is>
-          <t>InAppReviewControllerTest</t>
+          <t>TokenAuthenticatorTest</t>
         </is>
       </c>
       <c r="B8" s="13" t="inlineStr">
         <is>
-          <t>JVM</t>
+          <t>JVM + MockWebServer</t>
         </is>
       </c>
       <c r="C8" s="13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D8" s="13" t="inlineStr">
         <is>
-          <t>Đủ điều kiện mới hỏi; lỗi Play không làm crash.</t>
+          <t>Refresh 1 lần khi 401, không lặp vô hạn.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="13" t="inlineStr">
         <is>
-          <t>InAppUpdateControllerTest</t>
+          <t>InAppReviewControllerTest</t>
         </is>
       </c>
       <c r="B9" s="13" t="inlineStr">
@@ -5581,18 +7402,18 @@
         </is>
       </c>
       <c r="C9" s="13" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D9" s="13" t="inlineStr">
         <is>
-          <t>Immediate/flexible, từ chối, đã tải xong, Play không khả dụng.</t>
+          <t>Đủ điều kiện mới hỏi; lỗi Play không làm crash.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="13" t="inlineStr">
         <is>
-          <t>ReviewPolicyTest</t>
+          <t>InAppUpdateControllerTest</t>
         </is>
       </c>
       <c r="B10" s="13" t="inlineStr">
@@ -5601,18 +7422,18 @@
         </is>
       </c>
       <c r="C10" s="13" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D10" s="13" t="inlineStr">
         <is>
-          <t>Ngưỡng lần mở, số ngày, cooldown.</t>
+          <t>Immediate/flexible, từ chối, đã tải xong, Play không khả dụng.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="13" t="inlineStr">
         <is>
-          <t>UpdatePolicyTest</t>
+          <t>ReviewPolicyTest</t>
         </is>
       </c>
       <c r="B11" s="13" t="inlineStr">
@@ -5621,43 +7442,43 @@
         </is>
       </c>
       <c r="C11" s="13" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D11" s="13" t="inlineStr">
         <is>
-          <t>Chọn kiểu cập nhật theo priority và số ngày.</t>
+          <t>Ngưỡng lần mở, số ngày, cooldown.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="13" t="inlineStr">
         <is>
-          <t>AppDatabaseMigrationTest</t>
+          <t>UpdatePolicyTest</t>
         </is>
       </c>
       <c r="B12" s="13" t="inlineStr">
         <is>
-          <t>Robolectric</t>
+          <t>JVM</t>
         </is>
       </c>
       <c r="C12" s="13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D12" s="13" t="inlineStr">
         <is>
-          <t>Migrate mọi version, dữ liệu v1 còn nguyên, builder thật mở được.</t>
+          <t>Chọn kiểu cập nhật theo priority và số ngày.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="13" t="inlineStr">
         <is>
-          <t>AppPreferencesSerializerTest</t>
+          <t>AppDatabaseMigrationTest</t>
         </is>
       </c>
       <c r="B13" s="13" t="inlineStr">
         <is>
-          <t>JVM</t>
+          <t>Robolectric</t>
         </is>
       </c>
       <c r="C13" s="13" t="n">
@@ -5665,14 +7486,14 @@
       </c>
       <c r="D13" s="13" t="inlineStr">
         <is>
-          <t>Mã hoá round trip, file hỏng, file cũ vẫn đọc được.</t>
+          <t>Migrate mọi version (gồm v1→v2), dữ liệu v1 còn nguyên, builder thật mở được.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="13" t="inlineStr">
         <is>
-          <t>AuthRepositoryImplTest</t>
+          <t>AppPreferencesSerializerTest</t>
         </is>
       </c>
       <c r="B14" s="13" t="inlineStr">
@@ -5681,38 +7502,38 @@
         </is>
       </c>
       <c r="C14" s="13" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D14" s="13" t="inlineStr">
         <is>
-          <t>Login/register/refresh/logout, không nuốt lỗi huỷ.</t>
+          <t>Mã hoá round trip, file hỏng, file cũ vẫn đọc được.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="13" t="inlineStr">
         <is>
-          <t>AuthTokenRefresherTest</t>
+          <t>WorkerAiClientTest</t>
         </is>
       </c>
       <c r="B15" s="13" t="inlineStr">
         <is>
-          <t>JVM</t>
+          <t>JVM + MockWebServer</t>
         </is>
       </c>
       <c r="C15" s="13" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D15" s="13" t="inlineStr">
         <is>
-          <t>Mất mạng giữ phiên, bị từ chối thì đăng xuất.</t>
+          <t>Gửi task + ảnh, quota, 429/422/403/503, sai schema, báo cáo, không phiên khi offline.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="13" t="inlineStr">
         <is>
-          <t>FakeAuthRepositoryTest</t>
+          <t>FakeAiClientTest</t>
         </is>
       </c>
       <c r="B16" s="13" t="inlineStr">
@@ -5725,54 +7546,54 @@
       </c>
       <c r="D16" s="13" t="inlineStr">
         <is>
-          <t>Phiên demo.</t>
+          <t>Kết quả mẫu, đếm quota, hết lượt, task lạ.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="13" t="inlineStr">
         <is>
-          <t>RetrofitAuthBackendTest</t>
+          <t>ImageSizingTest</t>
         </is>
       </c>
       <c r="B17" s="13" t="inlineStr">
         <is>
-          <t>JVM + MockWebServer</t>
+          <t>JVM</t>
         </is>
       </c>
       <c r="C17" s="13" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D17" s="13" t="inlineStr">
         <is>
-          <t>Map 401/503/JSON sai/mất kết nối sang AppError.</t>
+          <t>Subsample, fit giữ tỉ lệ, không phóng to.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="13" t="inlineStr">
         <is>
-          <t>AuthSessionUseCasesTest</t>
+          <t>ImagePreprocessorTest</t>
         </is>
       </c>
       <c r="B18" s="13" t="inlineStr">
         <is>
-          <t>JVM</t>
+          <t>Robolectric (native graphics)</t>
         </is>
       </c>
       <c r="C18" s="13" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D18" s="13" t="inlineStr">
         <is>
-          <t>LogoutUseCase.</t>
+          <t>Giải mã, thu nhỏ, xoay EXIF, xoá GPS, từ chối file không phải ảnh.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="13" t="inlineStr">
         <is>
-          <t>LoginUseCaseTest</t>
+          <t>ScanViewModelTest</t>
         </is>
       </c>
       <c r="B19" s="13" t="inlineStr">
@@ -5781,18 +7602,18 @@
         </is>
       </c>
       <c r="C19" s="13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D19" s="13" t="inlineStr">
         <is>
-          <t>Validate email, mật khẩu.</t>
+          <t>Quét thành công lưu lịch sử, ảnh lỗi, hết lượt, báo cáo.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="13" t="inlineStr">
         <is>
-          <t>RegisterUseCaseTest</t>
+          <t>AuthRepositoryImplTest</t>
         </is>
       </c>
       <c r="B20" s="13" t="inlineStr">
@@ -5801,337 +7622,249 @@
         </is>
       </c>
       <c r="C20" s="13" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D20" s="13" t="inlineStr">
         <is>
-          <t>Tên hiển thị bắt buộc, chuẩn hoá dữ liệu.</t>
+          <t>Phiên ẩn danh, nâng cấp giữ uid, đổi tài khoản xoá dữ liệu, refresh, đăng xuất → ẩn danh mới.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="13" t="inlineStr">
         <is>
+          <t>AuthTokenRefresherTest</t>
+        </is>
+      </c>
+      <c r="B21" s="13" t="inlineStr">
+        <is>
+          <t>JVM</t>
+        </is>
+      </c>
+      <c r="C21" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="D21" s="13" t="inlineStr">
+        <is>
+          <t>Mất mạng giữ phiên, bị từ chối thì đăng xuất.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="13" t="inlineStr">
+        <is>
+          <t>FakeAuthRepositoryTest</t>
+        </is>
+      </c>
+      <c r="B22" s="13" t="inlineStr">
+        <is>
+          <t>JVM</t>
+        </is>
+      </c>
+      <c r="C22" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="D22" s="13" t="inlineStr">
+        <is>
+          <t>Phiên ẩn danh demo, đăng nhập, nâng cấp, đăng xuất.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="13" t="inlineStr">
+        <is>
+          <t>RetrofitAuthBackendTest</t>
+        </is>
+      </c>
+      <c r="B23" s="13" t="inlineStr">
+        <is>
+          <t>JVM + MockWebServer</t>
+        </is>
+      </c>
+      <c r="C23" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="D23" s="13" t="inlineStr">
+        <is>
+          <t>Map 401/503/JSON sai/mất kết nối sang AppError.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="13" t="inlineStr">
+        <is>
+          <t>AuthSessionUseCasesTest</t>
+        </is>
+      </c>
+      <c r="B24" s="13" t="inlineStr">
+        <is>
+          <t>JVM</t>
+        </is>
+      </c>
+      <c r="C24" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" s="13" t="inlineStr">
+        <is>
+          <t>LogoutUseCase.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="13" t="inlineStr">
+        <is>
+          <t>LoginUseCaseTest</t>
+        </is>
+      </c>
+      <c r="B25" s="13" t="inlineStr">
+        <is>
+          <t>JVM</t>
+        </is>
+      </c>
+      <c r="C25" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="D25" s="13" t="inlineStr">
+        <is>
+          <t>Validate email, mật khẩu.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="13" t="inlineStr">
+        <is>
+          <t>RegisterUseCaseTest</t>
+        </is>
+      </c>
+      <c r="B26" s="13" t="inlineStr">
+        <is>
+          <t>JVM</t>
+        </is>
+      </c>
+      <c r="C26" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="D26" s="13" t="inlineStr">
+        <is>
+          <t>Tên hiển thị bắt buộc, chuẩn hoá dữ liệu.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="13" t="inlineStr">
+        <is>
           <t>LoginViewModelTest</t>
         </is>
       </c>
-      <c r="B21" s="13" t="inlineStr">
+      <c r="B27" s="13" t="inlineStr">
         <is>
           <t>JVM</t>
         </is>
       </c>
-      <c r="C21" s="13" t="n">
+      <c r="C27" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="D21" s="13" t="inlineStr">
+      <c r="D27" s="13" t="inlineStr">
         <is>
           <t>Thành công phát event, thất bại hiện lỗi.</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="14" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="13" t="inlineStr">
+        <is>
+          <t>worker: auth.test.ts</t>
+        </is>
+      </c>
+      <c r="B28" s="13" t="inlineStr">
+        <is>
+          <t>Vitest trong workerd</t>
+        </is>
+      </c>
+      <c r="C28" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="D28" s="13" t="inlineStr">
+        <is>
+          <t>ID token hết hạn/sai issuer/sai audience; App Check thiếu/sai app; chế độ monitor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="13" t="inlineStr">
+        <is>
+          <t>worker: run.test.ts</t>
+        </is>
+      </c>
+      <c r="B29" s="13" t="inlineStr">
+        <is>
+          <t>Vitest trong workerd</t>
+        </is>
+      </c>
+      <c r="C29" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="D29" s="13" t="inlineStr">
+        <is>
+          <t>Gọi Gemini đúng định dạng, quota, bị chặn vẫn tính lượt, lỗi/sai schema hoàn lượt, chặn task lạ và ảnh sai.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="13" t="inlineStr">
+        <is>
+          <t>worker: report.test.ts</t>
+        </is>
+      </c>
+      <c r="B30" s="13" t="inlineStr">
+        <is>
+          <t>Vitest trong workerd</t>
+        </is>
+      </c>
+      <c r="C30" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="D30" s="13" t="inlineStr">
+        <is>
+          <t>Ghi D1, body sai, giới hạn báo cáo/ngày, routing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="13" t="inlineStr">
+        <is>
+          <t>worker: day.test.ts</t>
+        </is>
+      </c>
+      <c r="B31" s="13" t="inlineStr">
+        <is>
+          <t>Vitest trong workerd</t>
+        </is>
+      </c>
+      <c r="C31" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="D31" s="13" t="inlineStr">
+        <is>
+          <t>Ngày quota theo giờ VN, đổi ngày lúc 0h, qua tháng.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="14" t="inlineStr">
         <is>
           <t>Tổng</t>
         </is>
       </c>
-      <c r="B22" s="15" t="n"/>
-      <c r="C22" s="14">
-        <f>SUM(C2:C21)</f>
+      <c r="B32" s="15" t="n"/>
+      <c r="C32" s="14">
+        <f>SUM(C2:C31)</f>
         <v/>
       </c>
-      <c r="D22" s="15" t="n"/>
+      <c r="D32" s="15" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D21"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C16"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="80" customWidth="1" min="2" max="2"/>
-    <col width="66" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="10" t="inlineStr">
-        <is>
-          <t>Chủ đề</t>
-        </is>
-      </c>
-      <c r="B1" s="10" t="inlineStr">
-        <is>
-          <t>Quy tắc</t>
-        </is>
-      </c>
-      <c r="C1" s="10" t="inlineStr">
-        <is>
-          <t>Vì sao</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="11" t="inlineStr">
-        <is>
-          <t>Dữ liệu</t>
-        </is>
-      </c>
-      <c r="B2" s="12" t="inlineStr">
-        <is>
-          <t>AppPreferences chỉ thêm field vào cuối, luôn có giá trị mặc định.</t>
-        </is>
-      </c>
-      <c r="C2" s="12" t="inlineStr">
-        <is>
-          <t>ProtoBuf đánh số field theo thứ tự; đổi thứ tự làm hỏng dữ liệu người dùng.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="13" t="inlineStr">
-        <is>
-          <t>Dữ liệu</t>
-        </is>
-      </c>
-      <c r="B3" s="13" t="inlineStr">
-        <is>
-          <t>Đổi schema Room phải có Migration + test.</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>Migration sai làm crash app với mọi người dùng cũ.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="11" t="inlineStr">
-        <is>
-          <t>Lỗi</t>
-        </is>
-      </c>
-      <c r="B4" s="12" t="inlineStr">
-        <is>
-          <t>Không hiển thị Throwable.message cho người dùng; dùng AppError + toUserMessage().</t>
-        </is>
-      </c>
-      <c r="C4" s="12" t="inlineStr">
-        <is>
-          <t>Thông báo chưa dịch, lộ chi tiết kỹ thuật.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="11" t="inlineStr">
-        <is>
-          <t>Coroutine</t>
-        </is>
-      </c>
-      <c r="B5" s="12" t="inlineStr">
-        <is>
-          <t>Dùng suspendRunCatching, không dùng runCatching trong hàm suspend.</t>
-        </is>
-      </c>
-      <c r="C5" s="12" t="inlineStr">
-        <is>
-          <t>runCatching nuốt CancellationException.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="11" t="inlineStr">
-        <is>
-          <t>Bảo mật</t>
-        </is>
-      </c>
-      <c r="B6" s="12" t="inlineStr">
-        <is>
-          <t>Token chỉ nằm trong DataStore mã hoá; không log header Authorization.</t>
-        </is>
-      </c>
-      <c r="C6" s="12" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="13" t="inlineStr">
-        <is>
-          <t>Bảo mật</t>
-        </is>
-      </c>
-      <c r="B7" s="13" t="inlineStr">
-        <is>
-          <t>Không commit keystore, keystore.properties, google-services.json.</t>
-        </is>
-      </c>
-      <c r="C7" s="13" t="inlineStr">
-        <is>
-          <t>Đã có trong .gitignore.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="11" t="inlineStr">
-        <is>
-          <t>Quảng cáo</t>
-        </is>
-      </c>
-      <c r="B8" s="12" t="inlineStr">
-        <is>
-          <t>Bản debug luôn dùng ID quảng cáo test.</t>
-        </is>
-      </c>
-      <c r="C8" s="12" t="inlineStr">
-        <is>
-          <t>Tự click quảng cáo thật có thể bị khoá tài khoản AdMob.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="13" t="inlineStr">
-        <is>
-          <t>Quảng cáo</t>
-        </is>
-      </c>
-      <c r="B9" s="13" t="inlineStr">
-        <is>
-          <t>Không hiện quảng cáo xen kẽ lúc mở app hay giữa thao tác.</t>
-        </is>
-      </c>
-      <c r="C9" s="13" t="inlineStr">
-        <is>
-          <t>Vi phạm chính sách, kéo điểm đánh giá xuống.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="13" t="inlineStr">
-        <is>
-          <t>Quảng cáo</t>
-        </is>
-      </c>
-      <c r="B10" s="13" t="inlineStr">
-        <is>
-          <t>Manifest luôn phải có App ID AdMob.</t>
-        </is>
-      </c>
-      <c r="C10" s="13" t="inlineStr">
-        <is>
-          <t>Thiếu thì app crash ngay khi khởi động.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="11" t="inlineStr">
-        <is>
-          <t>Đánh giá</t>
-        </is>
-      </c>
-      <c r="B11" s="12" t="inlineStr">
-        <is>
-          <t>Không gắn In-App Review vào nút bấm.</t>
-        </is>
-      </c>
-      <c r="C11" s="12" t="inlineStr">
-        <is>
-          <t>Google có hạn mức, hộp thoại có thể không hiện.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="11" t="inlineStr">
-        <is>
-          <t>Compose</t>
-        </is>
-      </c>
-      <c r="B12" s="12" t="inlineStr">
-        <is>
-          <t>Composable công khai phải nhận modifier; callback đặt tên thì hiện tại (onLoginSuccess, không onAuthenticated).</t>
-        </is>
-      </c>
-      <c r="C12" s="12" t="inlineStr">
-        <is>
-          <t>Luật Compose của ktlint bắt.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="11" t="inlineStr">
-        <is>
-          <t>DI</t>
-        </is>
-      </c>
-      <c r="B13" s="12" t="inlineStr">
-        <is>
-          <t>Thêm ViewModel nhớ khai báo viewModelOf(...).</t>
-        </is>
-      </c>
-      <c r="C13" s="12" t="inlineStr">
-        <is>
-          <t>KoinModulesTest không bắt được lỗi quên khai báo ViewModel.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="11" t="inlineStr">
-        <is>
-          <t>Build</t>
-        </is>
-      </c>
-      <c r="B14" s="12" t="inlineStr">
-        <is>
-          <t>Không nâng Compose BOM lên bản dùng Compose 1.12+ khi chưa nâng compileSdk 37.</t>
-        </is>
-      </c>
-      <c r="C14" s="12" t="inlineStr">
-        <is>
-          <t>Build lỗi.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="13" t="inlineStr">
-        <is>
-          <t>Build</t>
-        </is>
-      </c>
-      <c r="B15" s="13" t="inlineStr">
-        <is>
-          <t>detekt 1.23.8 cần đoạn ghim Kotlin riêng trong build.gradle.kts.</t>
-        </is>
-      </c>
-      <c r="C15" s="13" t="inlineStr">
-        <is>
-          <t>Bỏ đoạn đó thì detekt lỗi với Kotlin 2.2.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="11" t="inlineStr">
-        <is>
-          <t>Thiết bị</t>
-        </is>
-      </c>
-      <c r="B16" s="12" t="inlineStr">
-        <is>
-          <t>Không dùng emulator (chưa cài); hỏi trước khi chạy trên điện thoại.</t>
-        </is>
-      </c>
-      <c r="C16" s="12" t="inlineStr">
-        <is>
-          <t>Thoả thuận khi làm việc.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:C16"/>
+  <autoFilter ref="A1:D31"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>